--- a/public/DataMahasiswa/user.xlsx
+++ b/public/DataMahasiswa/user.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp_oh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDC67FA-B20C-4EA9-ABB2-B810F884072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43167912-F30E-4272-B3F3-86F4C91E598D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>user</t>
   </si>
   <si>
-    <t>user@gmail.com</t>
+    <t>rehan</t>
+  </si>
+  <si>
+    <t>rehan@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -385,18 +388,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -405,10 +408,7 @@
         <v>0</v>
       </c>
       <c r="E1">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
